--- a/data/samples/HR_Current.xlsx
+++ b/data/samples/HR_Current.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01D89CFD-3800-41AA-A992-036A7FA27AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43EF4663-B5EF-418E-A41E-6F8447FD16A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{FE84FFEF-E308-49D3-B888-E53A69C82396}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE84FFEF-E308-49D3-B888-E53A69C82396}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="261">
   <si>
     <t>Employee Code</t>
   </si>
@@ -793,6 +793,21 @@
   </si>
   <si>
     <t>ريان حاتم المحمدي</t>
+  </si>
+  <si>
+    <t>Location Arabic Name</t>
+  </si>
+  <si>
+    <t>المدينة - الحربي</t>
+  </si>
+  <si>
+    <t>المدينة - جبل احد</t>
+  </si>
+  <si>
+    <t>المدينة - موارد</t>
+  </si>
+  <si>
+    <t>المدينة - ارض النظافة</t>
   </si>
 </sst>
 </file>
@@ -829,9 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1148,10 +1161,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4C072F-7B15-4B0B-91DE-D9092BFB02C0}">
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="49.5703125" customWidth="1"/>
+    <col min="7" max="7" width="27.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1206,8 +1223,11 @@
       <c r="S1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1256,8 +1276,11 @@
       <c r="R2" s="1">
         <v>45729</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1306,8 +1329,11 @@
       <c r="R3" s="1">
         <v>46216</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1356,8 +1382,11 @@
       <c r="R4" s="1">
         <v>46006</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1409,8 +1438,11 @@
       <c r="R5" s="1">
         <v>45965</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1462,8 +1494,11 @@
       <c r="R6" s="1">
         <v>45115</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1515,8 +1550,11 @@
       <c r="R7" s="1">
         <v>45117</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1568,8 +1606,11 @@
       <c r="R8" s="1">
         <v>45661</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1621,8 +1662,11 @@
       <c r="R9" s="1">
         <v>45979</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1674,8 +1718,11 @@
       <c r="R10" s="1">
         <v>45783</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1730,8 +1777,11 @@
       <c r="S11" s="1">
         <v>48876</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1783,8 +1833,11 @@
       <c r="R12" s="1">
         <v>45652</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1839,8 +1892,11 @@
       <c r="S13" s="1">
         <v>48099</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1895,8 +1951,11 @@
       <c r="S14" s="1">
         <v>49191</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1948,8 +2007,11 @@
       <c r="R15" s="1">
         <v>44933</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2001,8 +2063,11 @@
       <c r="R16" s="1">
         <v>45698</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2054,8 +2119,11 @@
       <c r="R17" s="1">
         <v>45652</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2107,8 +2175,11 @@
       <c r="R18" s="1">
         <v>45673</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2160,8 +2231,11 @@
       <c r="R19" s="1">
         <v>45006</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2213,8 +2287,11 @@
       <c r="R20" s="1">
         <v>46250</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2269,8 +2346,11 @@
       <c r="S21" s="1">
         <v>48992</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2322,8 +2402,11 @@
       <c r="R22" s="1">
         <v>45661</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2375,8 +2458,11 @@
       <c r="R23" s="1">
         <v>45719</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2428,8 +2514,11 @@
       <c r="R24" s="1">
         <v>45746</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2481,8 +2570,11 @@
       <c r="R25" s="1">
         <v>45718</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2534,8 +2626,11 @@
       <c r="R26" s="1">
         <v>45440</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2587,8 +2682,11 @@
       <c r="R27" s="1">
         <v>46089</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2637,8 +2735,11 @@
       <c r="P28" s="1">
         <v>45943</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2687,8 +2788,11 @@
       <c r="P29" s="1">
         <v>45943</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2740,8 +2844,11 @@
       <c r="S30" s="1">
         <v>48602</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2790,8 +2897,11 @@
       <c r="P31" s="1">
         <v>45943</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2843,8 +2953,11 @@
       <c r="R32" s="1">
         <v>45858</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2893,8 +3006,11 @@
       <c r="P33" s="1">
         <v>45963</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2946,8 +3062,11 @@
       <c r="S34" s="1">
         <v>48500</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2993,8 +3112,11 @@
       <c r="P35" s="1">
         <v>45991</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3040,8 +3162,11 @@
       <c r="P36" s="1">
         <v>46203</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3090,8 +3215,11 @@
       <c r="P37" s="1">
         <v>46232</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3140,8 +3268,11 @@
       <c r="P38" s="1">
         <v>46232</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3187,8 +3318,11 @@
       <c r="P39" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3234,8 +3368,11 @@
       <c r="P40" s="1">
         <v>46222</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3281,8 +3418,11 @@
       <c r="P41" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3328,8 +3468,11 @@
       <c r="P42" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3375,8 +3518,11 @@
       <c r="P43" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3422,8 +3568,11 @@
       <c r="P44" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T44" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3469,8 +3618,11 @@
       <c r="P45" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T45" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3516,8 +3668,11 @@
       <c r="P46" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T46" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3563,8 +3718,11 @@
       <c r="P47" s="1">
         <v>46218</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T47" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3613,8 +3771,11 @@
       <c r="P48" s="1">
         <v>46307</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T48" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3660,8 +3821,11 @@
       <c r="P49" s="1">
         <v>46217</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T49" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3707,8 +3871,11 @@
       <c r="P50" s="1">
         <v>46217</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T50" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3757,2345 +3924,2229 @@
       <c r="R51" s="1">
         <v>46113</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="T51" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52">
         <v>1005</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" t="s">
         <v>133</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" t="s">
         <v>134</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" t="s">
         <v>135</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" t="s">
         <v>135</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" t="s">
         <v>136</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52">
         <v>14000</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52">
         <v>74.188400000000001</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52">
         <v>17</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M52" s="2" t="s">
+      <c r="L52" t="s">
+        <v>18</v>
+      </c>
+      <c r="M52" t="s">
         <v>137</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="1">
         <v>44639</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="1">
         <v>46598</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="1">
         <v>44729</v>
       </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="3">
+      <c r="R52" s="1">
         <v>46574</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="1">
         <v>46218</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53">
         <v>1033</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>138</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
         <v>139</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53">
         <v>1</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" t="s">
         <v>135</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" t="s">
         <v>135</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" t="s">
         <v>140</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53">
         <v>9893</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53">
         <v>123.0984</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53">
         <v>16.5</v>
       </c>
-      <c r="L53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M53" s="2" t="s">
+      <c r="L53" t="s">
+        <v>18</v>
+      </c>
+      <c r="M53" t="s">
         <v>141</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53" s="1">
         <v>44671</v>
       </c>
-      <c r="O53" s="2"/>
-      <c r="P53" s="3">
+      <c r="P53" s="1">
         <v>44761</v>
       </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54">
         <v>1092</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" t="s">
         <v>143</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54">
         <v>5</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" t="s">
         <v>144</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54">
         <v>4947</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54">
         <v>7.1691000000000003</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54">
         <v>-2</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M54" s="2" t="s">
+      <c r="L54" t="s">
+        <v>18</v>
+      </c>
+      <c r="M54" t="s">
         <v>141</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="1">
         <v>44901</v>
       </c>
-      <c r="O54" s="2"/>
-      <c r="P54" s="3">
+      <c r="P54" s="1">
         <v>44991</v>
       </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="2"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55">
         <v>1226</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55">
         <v>4</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" t="s">
         <v>20</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>148</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" t="s">
         <v>149</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55">
         <v>5276</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55">
         <v>24.863326669999999</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K55">
         <v>1</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M55" s="2" t="s">
+      <c r="L55" t="s">
+        <v>18</v>
+      </c>
+      <c r="M55" t="s">
         <v>141</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55" s="1">
         <v>44944</v>
       </c>
-      <c r="O55" s="2"/>
-      <c r="P55" s="3">
+      <c r="P55" s="1">
         <v>45034</v>
       </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56">
         <v>1249</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" t="s">
         <v>150</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56">
         <v>4</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" t="s">
         <v>22</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" t="s">
         <v>152</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I56">
         <v>3000</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56">
         <v>19.97716333</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56">
         <v>4</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M56" s="2" t="s">
+      <c r="L56" t="s">
+        <v>18</v>
+      </c>
+      <c r="M56" t="s">
         <v>19</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56" s="1">
         <v>44808</v>
       </c>
-      <c r="O56" s="3">
+      <c r="O56" s="1">
         <v>46536</v>
       </c>
-      <c r="P56" s="3">
+      <c r="P56" s="1">
         <v>44986</v>
       </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" s="3">
+      <c r="R56" s="1">
         <v>46583</v>
       </c>
-      <c r="S56" s="3">
+      <c r="S56" s="1">
         <v>46264</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57">
         <v>1250</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57">
         <v>4</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" t="s">
         <v>20</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" t="s">
         <v>23</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" t="s">
         <v>152</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I57">
         <v>3000</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57">
         <v>37.383643329999998</v>
       </c>
-      <c r="K57" s="2">
+      <c r="K57">
         <v>1</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M57" s="2" t="s">
+      <c r="L57" t="s">
+        <v>18</v>
+      </c>
+      <c r="M57" t="s">
         <v>19</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="1">
         <v>44643</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="1">
         <v>46509</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="1">
         <v>44821</v>
       </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="3">
+      <c r="R57" s="1">
         <v>46613</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="1">
         <v>49512</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58">
         <v>1266</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" t="s">
         <v>155</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>156</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58">
         <v>5</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" t="s">
         <v>24</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" t="s">
         <v>157</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" t="s">
         <v>145</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I58">
         <v>4947</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58">
         <v>8.2329733330000003</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58">
         <v>0.5</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M58" s="2" t="s">
+      <c r="L58" t="s">
+        <v>18</v>
+      </c>
+      <c r="M58" t="s">
         <v>141</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="1">
         <v>45045</v>
       </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="3">
+      <c r="P58" s="1">
         <v>45134</v>
       </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59">
         <v>1335</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>158</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59">
         <v>5</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" t="s">
         <v>144</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" t="s">
         <v>145</v>
       </c>
-      <c r="I59" s="2">
+      <c r="I59">
         <v>4947</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59">
         <v>15.65621333</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K59">
         <v>1.5</v>
       </c>
-      <c r="L59" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M59" s="2" t="s">
+      <c r="L59" t="s">
+        <v>18</v>
+      </c>
+      <c r="M59" t="s">
         <v>141</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="1">
         <v>45132</v>
       </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="3">
+      <c r="P59" s="1">
         <v>45221</v>
       </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60">
         <v>1338</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" t="s">
         <v>160</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" t="s">
         <v>161</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60">
         <v>4</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" t="s">
         <v>22</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" t="s">
         <v>162</v>
       </c>
-      <c r="I60" s="2">
+      <c r="I60">
         <v>3600</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60">
         <v>5.4177966670000002</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K60">
         <v>1</v>
       </c>
-      <c r="L60" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M60" s="2" t="s">
+      <c r="L60" t="s">
+        <v>18</v>
+      </c>
+      <c r="M60" t="s">
         <v>19</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="1">
         <v>45139</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="1">
         <v>46674</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="1">
         <v>45228</v>
       </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="3">
+      <c r="R60" s="1">
         <v>46372</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="1">
         <v>46896</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61">
         <v>1341</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" t="s">
         <v>163</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
         <v>164</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61">
         <v>3</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" t="s">
         <v>135</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" t="s">
         <v>135</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" t="s">
         <v>165</v>
       </c>
-      <c r="I61" s="2">
+      <c r="I61">
         <v>4500</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61">
         <v>11.14739067</v>
       </c>
-      <c r="K61" s="2">
+      <c r="K61">
         <v>1</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M61" s="2" t="s">
+      <c r="L61" t="s">
+        <v>18</v>
+      </c>
+      <c r="M61" t="s">
         <v>137</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61" s="1">
         <v>45143</v>
       </c>
-      <c r="O61" s="3">
+      <c r="O61" s="1">
         <v>46394</v>
       </c>
-      <c r="P61" s="3">
+      <c r="P61" s="1">
         <v>45232</v>
       </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="3">
+      <c r="R61" s="1">
         <v>46465</v>
       </c>
-      <c r="S61" s="2"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62">
         <v>1352</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" t="s">
         <v>166</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" t="s">
         <v>167</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62">
         <v>4</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" t="s">
         <v>21</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" t="s">
         <v>168</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" t="s">
         <v>149</v>
       </c>
-      <c r="I62" s="2">
+      <c r="I62">
         <v>5643</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62">
         <v>7.2304033329999999</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K62">
         <v>1</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L62" t="s">
         <v>169</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M62" t="s">
         <v>141</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="1">
         <v>45154</v>
       </c>
-      <c r="O62" s="2"/>
-      <c r="P62" s="3">
+      <c r="P62" s="1">
         <v>45243</v>
       </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63">
         <v>1379</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" t="s">
         <v>170</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63">
         <v>4</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" t="s">
         <v>25</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" t="s">
         <v>172</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" t="s">
         <v>173</v>
       </c>
-      <c r="I63" s="2">
+      <c r="I63">
         <v>5167</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63">
         <v>14.178466670000001</v>
       </c>
-      <c r="K63" s="2">
+      <c r="K63">
         <v>1</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M63" s="2" t="s">
+      <c r="L63" t="s">
+        <v>18</v>
+      </c>
+      <c r="M63" t="s">
         <v>141</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63" s="1">
         <v>45175</v>
       </c>
-      <c r="O63" s="2"/>
-      <c r="P63" s="3">
+      <c r="P63" s="1">
         <v>45264</v>
       </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64">
         <v>1438</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" t="s">
         <v>174</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" t="s">
         <v>175</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64">
         <v>6</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" t="s">
         <v>176</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="H64" t="s">
         <v>177</v>
       </c>
-      <c r="I64" s="2">
+      <c r="I64">
         <v>4440</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64">
         <v>27.081389999999999</v>
       </c>
-      <c r="K64" s="2">
+      <c r="K64">
         <v>1</v>
       </c>
-      <c r="L64" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M64" s="2" t="s">
+      <c r="L64" t="s">
+        <v>18</v>
+      </c>
+      <c r="M64" t="s">
         <v>141</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64" s="1">
         <v>45214</v>
       </c>
-      <c r="O64" s="2"/>
-      <c r="P64" s="3">
+      <c r="P64" s="1">
         <v>45303</v>
       </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65">
         <v>1459</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" t="s">
         <v>178</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" t="s">
         <v>179</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65">
         <v>5</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" t="s">
         <v>180</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" t="s">
         <v>145</v>
       </c>
-      <c r="I65" s="2">
+      <c r="I65">
         <v>4727</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65">
         <v>16.385896670000001</v>
       </c>
-      <c r="K65" s="2">
+      <c r="K65">
         <v>2.5</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M65" s="2" t="s">
+      <c r="L65" t="s">
+        <v>18</v>
+      </c>
+      <c r="M65" t="s">
         <v>141</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65" s="1">
         <v>45231</v>
       </c>
-      <c r="O65" s="2"/>
-      <c r="P65" s="3">
+      <c r="P65" s="1">
         <v>45320</v>
       </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66">
         <v>1473</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" t="s">
         <v>181</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" t="s">
         <v>182</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66">
         <v>5</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" t="s">
         <v>21</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" t="s">
         <v>168</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="H66" t="s">
         <v>183</v>
       </c>
-      <c r="I66" s="2">
+      <c r="I66">
         <v>4837</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66">
         <v>29.385896670000001</v>
       </c>
-      <c r="K66" s="2">
+      <c r="K66">
         <v>3.5</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M66" s="2" t="s">
+      <c r="L66" t="s">
+        <v>18</v>
+      </c>
+      <c r="M66" t="s">
         <v>141</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="1">
         <v>45245</v>
       </c>
-      <c r="O66" s="2"/>
-      <c r="P66" s="3">
+      <c r="P66" s="1">
         <v>45334</v>
       </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67">
         <v>1512</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" t="s">
         <v>184</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" t="s">
         <v>185</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67">
         <v>4</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" t="s">
         <v>152</v>
       </c>
-      <c r="I67" s="2">
+      <c r="I67">
         <v>3250</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67">
         <v>32.353326670000001</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K67">
         <v>2</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M67" s="2" t="s">
+      <c r="L67" t="s">
+        <v>18</v>
+      </c>
+      <c r="M67" t="s">
         <v>19</v>
       </c>
-      <c r="N67" s="3">
+      <c r="N67" s="1">
         <v>45281</v>
       </c>
-      <c r="O67" s="3">
+      <c r="O67" s="1">
         <v>46625</v>
       </c>
-      <c r="P67" s="3">
+      <c r="P67" s="1">
         <v>45459</v>
       </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="3">
+      <c r="R67" s="1">
         <v>46569</v>
       </c>
-      <c r="S67" s="2"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68">
         <v>1860</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" t="s">
         <v>186</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" t="s">
         <v>187</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68">
         <v>5</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" t="s">
         <v>20</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" t="s">
         <v>148</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" t="s">
         <v>183</v>
       </c>
-      <c r="I68" s="2">
+      <c r="I68">
         <v>4617</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68">
         <v>19.908149999999999</v>
       </c>
-      <c r="K68" s="2">
+      <c r="K68">
         <v>2.5</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M68" s="2" t="s">
+      <c r="L68" t="s">
+        <v>18</v>
+      </c>
+      <c r="M68" t="s">
         <v>141</v>
       </c>
-      <c r="N68" s="3">
+      <c r="N68" s="1">
         <v>45627</v>
       </c>
-      <c r="O68" s="2"/>
-      <c r="P68" s="3">
+      <c r="P68" s="1">
         <v>45716</v>
       </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69">
         <v>1927</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" t="s">
         <v>188</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" t="s">
         <v>189</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69">
         <v>5</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" t="s">
         <v>180</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" t="s">
         <v>145</v>
       </c>
-      <c r="I69" s="2">
+      <c r="I69">
         <v>4507</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69">
         <v>21.247833329999999</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69">
         <v>2</v>
       </c>
-      <c r="L69" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M69" s="2" t="s">
+      <c r="L69" t="s">
+        <v>18</v>
+      </c>
+      <c r="M69" t="s">
         <v>141</v>
       </c>
-      <c r="N69" s="3">
+      <c r="N69" s="1">
         <v>45691</v>
       </c>
-      <c r="O69" s="2"/>
-      <c r="P69" s="3">
+      <c r="P69" s="1">
         <v>45780</v>
       </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70">
         <v>1928</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" t="s">
         <v>190</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" t="s">
         <v>191</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70">
         <v>5</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" t="s">
         <v>192</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="H70" t="s">
         <v>193</v>
       </c>
-      <c r="I70" s="2">
+      <c r="I70">
         <v>3000</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70">
         <v>42.117199999999997</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70">
         <v>4</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M70" s="2" t="s">
+      <c r="L70" t="s">
+        <v>18</v>
+      </c>
+      <c r="M70" t="s">
         <v>137</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N70" s="1">
         <v>45697</v>
       </c>
-      <c r="O70" s="2"/>
-      <c r="P70" s="3">
+      <c r="P70" s="1">
         <v>45786</v>
       </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="3">
+      <c r="R70" s="1">
         <v>46394</v>
       </c>
-      <c r="S70" s="2"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71">
         <v>1935</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" t="s">
         <v>194</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" t="s">
         <v>195</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71">
         <v>5</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" t="s">
         <v>25</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" t="s">
         <v>172</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" t="s">
         <v>145</v>
       </c>
-      <c r="I71" s="2">
+      <c r="I71">
         <v>4507</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71">
         <v>11.822340000000001</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71">
         <v>1</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M71" s="2" t="s">
+      <c r="L71" t="s">
+        <v>18</v>
+      </c>
+      <c r="M71" t="s">
         <v>141</v>
       </c>
-      <c r="N71" s="3">
+      <c r="N71" s="1">
         <v>45698</v>
       </c>
-      <c r="O71" s="2"/>
-      <c r="P71" s="3">
+      <c r="P71" s="1">
         <v>45787</v>
       </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72">
         <v>1939</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" t="s">
         <v>196</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" t="s">
         <v>197</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72">
         <v>5</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" t="s">
         <v>25</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" t="s">
         <v>198</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" t="s">
         <v>183</v>
       </c>
-      <c r="I72" s="2">
+      <c r="I72">
         <v>4617</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72">
         <v>29.251706670000001</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72">
         <v>1.5</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M72" s="2" t="s">
+      <c r="L72" t="s">
+        <v>18</v>
+      </c>
+      <c r="M72" t="s">
         <v>141</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="1">
         <v>45698</v>
       </c>
-      <c r="O72" s="2"/>
-      <c r="P72" s="3">
+      <c r="P72" s="1">
         <v>45787</v>
       </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73">
         <v>1940</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" t="s">
         <v>199</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" t="s">
         <v>200</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73">
         <v>5</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" t="s">
         <v>198</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="H73" t="s">
         <v>183</v>
       </c>
-      <c r="I73" s="2">
+      <c r="I73">
         <v>4617</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73">
         <v>20.63170667</v>
       </c>
-      <c r="K73" s="2">
+      <c r="K73">
         <v>1</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M73" s="2" t="s">
+      <c r="L73" t="s">
+        <v>18</v>
+      </c>
+      <c r="M73" t="s">
         <v>141</v>
       </c>
-      <c r="N73" s="3">
+      <c r="N73" s="1">
         <v>45701</v>
       </c>
-      <c r="O73" s="2"/>
-      <c r="P73" s="3">
+      <c r="P73" s="1">
         <v>45790</v>
       </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74">
         <v>1941</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" t="s">
         <v>201</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" t="s">
         <v>202</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74">
         <v>5</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" t="s">
         <v>20</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" t="s">
         <v>148</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" t="s">
         <v>183</v>
       </c>
-      <c r="I74" s="2">
+      <c r="I74">
         <v>4617</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74">
         <v>26.689769999999999</v>
       </c>
-      <c r="K74" s="2">
+      <c r="K74">
         <v>1.5</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M74" s="2" t="s">
+      <c r="L74" t="s">
+        <v>18</v>
+      </c>
+      <c r="M74" t="s">
         <v>141</v>
       </c>
-      <c r="N74" s="3">
+      <c r="N74" s="1">
         <v>45706</v>
       </c>
-      <c r="O74" s="2"/>
-      <c r="P74" s="3">
+      <c r="P74" s="1">
         <v>45795</v>
       </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75">
         <v>1971</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" t="s">
         <v>203</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" t="s">
         <v>204</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75">
         <v>6</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" t="s">
         <v>24</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" t="s">
         <v>205</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H75" t="s">
         <v>177</v>
       </c>
-      <c r="I75" s="2">
+      <c r="I75">
         <v>4220</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75">
         <v>19.018149999999999</v>
       </c>
-      <c r="K75" s="2">
+      <c r="K75">
         <v>1.5</v>
       </c>
-      <c r="L75" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M75" s="2" t="s">
+      <c r="L75" t="s">
+        <v>18</v>
+      </c>
+      <c r="M75" t="s">
         <v>141</v>
       </c>
-      <c r="N75" s="3">
+      <c r="N75" s="1">
         <v>45724</v>
       </c>
-      <c r="O75" s="2"/>
-      <c r="P75" s="3">
+      <c r="P75" s="1">
         <v>45813</v>
       </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76">
         <v>1972</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" t="s">
         <v>206</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76">
         <v>5</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" t="s">
         <v>25</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" t="s">
         <v>198</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" t="s">
         <v>183</v>
       </c>
-      <c r="I76" s="2">
+      <c r="I76">
         <v>4617</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76">
         <v>28.947516669999999</v>
       </c>
-      <c r="K76" s="2">
+      <c r="K76">
         <v>3</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M76" s="2" t="s">
+      <c r="L76" t="s">
+        <v>18</v>
+      </c>
+      <c r="M76" t="s">
         <v>141</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="1">
         <v>45721</v>
       </c>
-      <c r="O76" s="2"/>
-      <c r="P76" s="3">
+      <c r="P76" s="1">
         <v>45810</v>
       </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77">
         <v>2078</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" t="s">
         <v>208</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77">
         <v>5</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" t="s">
         <v>148</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" t="s">
         <v>183</v>
       </c>
-      <c r="I77" s="2">
+      <c r="I77">
         <v>4617</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77">
         <v>17.40008667</v>
       </c>
-      <c r="K77" s="2">
+      <c r="K77">
         <v>1</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M77" s="2" t="s">
+      <c r="L77" t="s">
+        <v>18</v>
+      </c>
+      <c r="M77" t="s">
         <v>141</v>
       </c>
-      <c r="N77" s="3">
+      <c r="N77" s="1">
         <v>45858</v>
       </c>
-      <c r="O77" s="2"/>
-      <c r="P77" s="3">
+      <c r="P77" s="1">
         <v>46038</v>
       </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78">
         <v>2298</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" t="s">
         <v>210</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78">
         <v>5</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" t="s">
         <v>24</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" t="s">
         <v>157</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" t="s">
         <v>145</v>
       </c>
-      <c r="I78" s="2">
+      <c r="I78">
         <v>4287</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78">
         <v>11.49202333</v>
       </c>
-      <c r="K78" s="2">
+      <c r="K78">
         <v>2.5</v>
       </c>
-      <c r="L78" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M78" s="2" t="s">
+      <c r="L78" t="s">
+        <v>18</v>
+      </c>
+      <c r="M78" t="s">
         <v>141</v>
       </c>
-      <c r="N78" s="3">
+      <c r="N78" s="1">
         <v>46026</v>
       </c>
-      <c r="O78" s="2"/>
-      <c r="P78" s="3">
+      <c r="P78" s="1">
         <v>46204</v>
       </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79">
         <v>2350</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" t="s">
         <v>213</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79">
         <v>5</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="F79" t="s">
         <v>20</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" t="s">
         <v>214</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" t="s">
         <v>193</v>
       </c>
-      <c r="I79" s="2">
+      <c r="I79">
         <v>3000</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79">
         <v>29.5472</v>
       </c>
-      <c r="K79" s="2">
+      <c r="K79">
         <v>4.5</v>
       </c>
-      <c r="L79" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M79" s="2" t="s">
+      <c r="L79" t="s">
+        <v>18</v>
+      </c>
+      <c r="M79" t="s">
         <v>215</v>
       </c>
-      <c r="N79" s="3">
+      <c r="N79" s="1">
         <v>45904</v>
       </c>
-      <c r="O79" s="3">
+      <c r="O79" s="1">
         <v>46633</v>
       </c>
-      <c r="P79" s="3">
+      <c r="P79" s="1">
         <v>45993</v>
       </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="3">
+      <c r="R79" s="1">
         <v>46623</v>
       </c>
-      <c r="S79" s="3">
+      <c r="S79" s="1">
         <v>48850</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80">
         <v>2443</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" t="s">
         <v>216</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" t="s">
         <v>217</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80">
         <v>6</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" t="s">
         <v>20</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" t="s">
         <v>218</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" t="s">
         <v>177</v>
       </c>
-      <c r="I80" s="2">
+      <c r="I80">
         <v>4001</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80">
         <v>13.37832</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80">
         <v>1</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M80" s="2" t="s">
+      <c r="L80" t="s">
+        <v>18</v>
+      </c>
+      <c r="M80" t="s">
         <v>141</v>
       </c>
-      <c r="N80" s="3">
+      <c r="N80" s="1">
         <v>46167</v>
       </c>
-      <c r="O80" s="2"/>
-      <c r="P80" s="3">
+      <c r="P80" s="1">
         <v>46345</v>
       </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81">
         <v>2444</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" t="s">
         <v>219</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" t="s">
         <v>220</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81">
         <v>5</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" t="s">
         <v>25</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" t="s">
         <v>198</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" t="s">
         <v>183</v>
       </c>
-      <c r="I81" s="2">
+      <c r="I81">
         <v>4397</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81">
         <v>11.76796667</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81">
         <v>1</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M81" s="2" t="s">
+      <c r="L81" t="s">
+        <v>18</v>
+      </c>
+      <c r="M81" t="s">
         <v>141</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="1">
         <v>46194</v>
       </c>
-      <c r="O81" s="2"/>
-      <c r="P81" s="3">
+      <c r="P81" s="1">
         <v>46283</v>
       </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82">
         <v>2445</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" t="s">
         <v>221</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" t="s">
         <v>222</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82">
         <v>5</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" t="s">
         <v>21</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" t="s">
         <v>168</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" t="s">
         <v>183</v>
       </c>
-      <c r="I82" s="2">
+      <c r="I82">
         <v>4397</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82">
         <v>10.33441</v>
       </c>
-      <c r="K82" s="2">
+      <c r="K82">
         <v>1</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M82" s="2" t="s">
+      <c r="L82" t="s">
+        <v>18</v>
+      </c>
+      <c r="M82" t="s">
         <v>141</v>
       </c>
-      <c r="N82" s="3">
+      <c r="N82" s="1">
         <v>46200</v>
       </c>
-      <c r="O82" s="2"/>
-      <c r="P82" s="3">
+      <c r="P82" s="1">
         <v>46289</v>
       </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83">
         <v>2446</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" t="s">
         <v>223</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" t="s">
         <v>224</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83">
         <v>6</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" t="s">
         <v>25</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" t="s">
         <v>176</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" t="s">
         <v>177</v>
       </c>
-      <c r="I83" s="2">
+      <c r="I83">
         <v>4001</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83">
         <v>11.08666333</v>
       </c>
-      <c r="K83" s="2">
+      <c r="K83">
         <v>1</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M83" s="2" t="s">
+      <c r="L83" t="s">
+        <v>18</v>
+      </c>
+      <c r="M83" t="s">
         <v>141</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="1">
         <v>46204</v>
       </c>
-      <c r="O83" s="2"/>
-      <c r="P83" s="3">
+      <c r="P83" s="1">
         <v>46293</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84">
         <v>2447</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" t="s">
         <v>225</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" t="s">
         <v>226</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84">
         <v>6</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" t="s">
         <v>227</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" t="s">
         <v>177</v>
       </c>
-      <c r="I84" s="2">
+      <c r="I84">
         <v>4001</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84">
         <v>10.90085333</v>
       </c>
-      <c r="K84" s="2">
+      <c r="K84">
         <v>1</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M84" s="2" t="s">
+      <c r="L84" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" t="s">
         <v>141</v>
       </c>
-      <c r="N84" s="3">
+      <c r="N84" s="1">
         <v>46208</v>
       </c>
-      <c r="O84" s="2"/>
-      <c r="P84" s="3">
+      <c r="P84" s="1">
         <v>46297</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85">
         <v>2448</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" t="s">
         <v>228</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" t="s">
         <v>229</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85">
         <v>5</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F85" t="s">
         <v>24</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" t="s">
         <v>230</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" t="s">
         <v>183</v>
       </c>
-      <c r="I85" s="2">
+      <c r="I85">
         <v>4397</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85">
         <v>10.65310667</v>
       </c>
-      <c r="K85" s="2">
+      <c r="K85">
         <v>1</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M85" s="2" t="s">
+      <c r="L85" t="s">
+        <v>18</v>
+      </c>
+      <c r="M85" t="s">
         <v>141</v>
       </c>
-      <c r="N85" s="3">
+      <c r="N85" s="1">
         <v>46212</v>
       </c>
-      <c r="O85" s="2"/>
-      <c r="P85" s="3">
+      <c r="P85" s="1">
         <v>46301</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86">
         <v>2449</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" t="s">
         <v>231</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" t="s">
         <v>232</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86">
         <v>5</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" t="s">
         <v>24</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" t="s">
         <v>230</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H86" t="s">
         <v>183</v>
       </c>
-      <c r="I86" s="2">
+      <c r="I86">
         <v>4397</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86">
         <v>10.71504333</v>
       </c>
-      <c r="K86" s="2">
+      <c r="K86">
         <v>1</v>
       </c>
-      <c r="L86" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M86" s="2" t="s">
+      <c r="L86" t="s">
+        <v>18</v>
+      </c>
+      <c r="M86" t="s">
         <v>141</v>
       </c>
-      <c r="N86" s="3">
+      <c r="N86" s="1">
         <v>46211</v>
       </c>
-      <c r="O86" s="2"/>
-      <c r="P86" s="3">
+      <c r="P86" s="1">
         <v>46300</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87">
         <v>2451</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" t="s">
         <v>233</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" t="s">
         <v>234</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87">
         <v>5</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" t="s">
         <v>24</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" t="s">
         <v>230</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" t="s">
         <v>183</v>
       </c>
-      <c r="I87" s="2">
+      <c r="I87">
         <v>4397</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87">
         <v>10.65310667</v>
       </c>
-      <c r="K87" s="2">
+      <c r="K87">
         <v>1</v>
       </c>
-      <c r="L87" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M87" s="2" t="s">
+      <c r="L87" t="s">
+        <v>18</v>
+      </c>
+      <c r="M87" t="s">
         <v>141</v>
       </c>
-      <c r="N87" s="3">
+      <c r="N87" s="1">
         <v>46212</v>
       </c>
-      <c r="O87" s="2"/>
-      <c r="P87" s="3">
+      <c r="P87" s="1">
         <v>46301</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88">
         <v>2452</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" t="s">
         <v>235</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" t="s">
         <v>236</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88">
         <v>6</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F88" t="s">
         <v>24</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" t="s">
         <v>205</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" t="s">
         <v>177</v>
       </c>
-      <c r="I88" s="2">
+      <c r="I88">
         <v>4001</v>
       </c>
-      <c r="J88" s="2">
+      <c r="J88">
         <v>9.9718033330000004</v>
       </c>
-      <c r="K88" s="2">
+      <c r="K88">
         <v>1</v>
       </c>
-      <c r="L88" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M88" s="2" t="s">
+      <c r="L88" t="s">
+        <v>18</v>
+      </c>
+      <c r="M88" t="s">
         <v>141</v>
       </c>
-      <c r="N88" s="3">
+      <c r="N88" s="1">
         <v>46223</v>
       </c>
-      <c r="O88" s="2"/>
-      <c r="P88" s="3">
+      <c r="P88" s="1">
         <v>46312</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89">
         <v>2454</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" t="s">
         <v>237</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" t="s">
         <v>238</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89">
         <v>5</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F89" t="s">
         <v>24</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" t="s">
         <v>230</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" t="s">
         <v>183</v>
       </c>
-      <c r="I89" s="2">
+      <c r="I89">
         <v>4397</v>
       </c>
-      <c r="J89" s="2">
+      <c r="J89">
         <v>9.2904999999999998</v>
       </c>
-      <c r="K89" s="2">
+      <c r="K89">
         <v>1</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M89" s="2" t="s">
+      <c r="L89" t="s">
+        <v>18</v>
+      </c>
+      <c r="M89" t="s">
         <v>141</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="1">
         <v>46235</v>
       </c>
-      <c r="O89" s="2"/>
-      <c r="P89" s="3">
+      <c r="P89" s="1">
         <v>46418</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90">
         <v>2463</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" t="s">
         <v>239</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" t="s">
         <v>240</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90">
         <v>5</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" t="s">
         <v>21</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" t="s">
         <v>168</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H90" t="s">
         <v>183</v>
       </c>
-      <c r="I90" s="2">
+      <c r="I90">
         <v>4397</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90">
         <v>16.949770000000001</v>
       </c>
-      <c r="K90" s="2">
+      <c r="K90">
         <v>2</v>
       </c>
-      <c r="L90" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M90" s="2" t="s">
+      <c r="L90" t="s">
+        <v>18</v>
+      </c>
+      <c r="M90" t="s">
         <v>141</v>
       </c>
-      <c r="N90" s="3">
+      <c r="N90" s="1">
         <v>45953</v>
       </c>
-      <c r="O90" s="2"/>
-      <c r="P90" s="3">
+      <c r="P90" s="1">
         <v>46131</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91">
         <v>2474</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" t="s">
         <v>241</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" t="s">
         <v>242</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91">
         <v>6</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F91" t="s">
         <v>21</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" t="s">
         <v>227</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" t="s">
         <v>177</v>
       </c>
-      <c r="I91" s="2">
+      <c r="I91">
         <v>4000</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91">
         <v>9.9562133330000009</v>
       </c>
-      <c r="K91" s="2">
+      <c r="K91">
         <v>2</v>
       </c>
-      <c r="L91" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M91" s="2" t="s">
+      <c r="L91" t="s">
+        <v>18</v>
+      </c>
+      <c r="M91" t="s">
         <v>141</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="1">
         <v>45963</v>
       </c>
-      <c r="O91" s="2"/>
-      <c r="P91" s="3">
+      <c r="P91" s="1">
         <v>46141</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92">
         <v>2669</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" t="s">
         <v>243</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" t="s">
         <v>244</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92">
         <v>5</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F92" t="s">
         <v>20</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" t="s">
         <v>148</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" t="s">
         <v>183</v>
       </c>
-      <c r="I92" s="2">
+      <c r="I92">
         <v>4397</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92">
         <v>13.167833330000001</v>
       </c>
-      <c r="K92" s="2">
+      <c r="K92">
         <v>3</v>
       </c>
-      <c r="L92" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M92" s="2" t="s">
+      <c r="L92" t="s">
+        <v>18</v>
+      </c>
+      <c r="M92" t="s">
         <v>141</v>
       </c>
-      <c r="N92" s="3">
+      <c r="N92" s="1">
         <v>45998</v>
       </c>
-      <c r="O92" s="2"/>
-      <c r="P92" s="3">
+      <c r="P92" s="1">
         <v>46176</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93">
         <v>2693</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" t="s">
         <v>245</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" t="s">
         <v>246</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93">
         <v>6</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="F93" t="s">
         <v>21</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" t="s">
         <v>227</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" t="s">
         <v>177</v>
       </c>
-      <c r="I93" s="2">
+      <c r="I93">
         <v>4000</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93">
         <v>19.819733329999998</v>
       </c>
-      <c r="K93" s="2">
+      <c r="K93">
         <v>2</v>
       </c>
-      <c r="L93" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M93" s="2" t="s">
+      <c r="L93" t="s">
+        <v>18</v>
+      </c>
+      <c r="M93" t="s">
         <v>141</v>
       </c>
-      <c r="N93" s="3">
+      <c r="N93" s="1">
         <v>46056</v>
       </c>
-      <c r="O93" s="2"/>
-      <c r="P93" s="3">
+      <c r="P93" s="1">
         <v>46234</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94">
         <v>2708</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" t="s">
         <v>247</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" t="s">
         <v>248</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94">
         <v>6</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F94" t="s">
         <v>20</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" t="s">
         <v>218</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H94" t="s">
         <v>177</v>
       </c>
-      <c r="I94" s="2">
+      <c r="I94">
         <v>4000</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94">
         <v>13.99768667</v>
       </c>
-      <c r="K94" s="2">
+      <c r="K94">
         <v>0.5</v>
       </c>
-      <c r="L94" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M94" s="2" t="s">
+      <c r="L94" t="s">
+        <v>18</v>
+      </c>
+      <c r="M94" t="s">
         <v>141</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="1">
         <v>46157</v>
       </c>
-      <c r="O94" s="2"/>
-      <c r="P94" s="3">
+      <c r="P94" s="1">
         <v>46335</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95">
         <v>2772</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" t="s">
         <v>249</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" t="s">
         <v>250</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95">
         <v>5</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" t="s">
         <v>24</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" t="s">
         <v>251</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" t="s">
         <v>193</v>
       </c>
-      <c r="I95" s="2">
+      <c r="I95">
         <v>4947</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95">
         <v>7.4324000000000003</v>
       </c>
-      <c r="K95" s="2">
+      <c r="K95">
         <v>1</v>
       </c>
-      <c r="L95" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M95" s="2" t="s">
+      <c r="L95" t="s">
+        <v>18</v>
+      </c>
+      <c r="M95" t="s">
         <v>141</v>
       </c>
-      <c r="N95" s="3">
+      <c r="N95" s="1">
         <v>46266</v>
       </c>
-      <c r="O95" s="2"/>
-      <c r="P95" s="3">
+      <c r="P95" s="1">
         <v>46355</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96">
         <v>2773</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" t="s">
         <v>252</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" t="s">
         <v>253</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96">
         <v>6</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F96" t="s">
         <v>20</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" t="s">
         <v>218</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="H96" t="s">
         <v>177</v>
       </c>
-      <c r="I96" s="2">
+      <c r="I96">
         <v>4001</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96">
         <v>7.4324000000000003</v>
       </c>
-      <c r="K96" s="2">
+      <c r="K96">
         <v>1</v>
       </c>
-      <c r="L96" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M96" s="2" t="s">
+      <c r="L96" t="s">
+        <v>18</v>
+      </c>
+      <c r="M96" t="s">
         <v>141</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="1">
         <v>46266</v>
       </c>
-      <c r="O96" s="2"/>
-      <c r="P96" s="3">
+      <c r="P96" s="1">
         <v>46355</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97">
         <v>2778</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" t="s">
         <v>254</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" t="s">
         <v>255</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97">
         <v>6</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F97" t="s">
         <v>25</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G97" t="s">
         <v>176</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" t="s">
         <v>177</v>
       </c>
-      <c r="I97" s="2">
+      <c r="I97">
         <v>4001</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97">
         <v>7.4324000000000003</v>
       </c>
-      <c r="K97" s="2">
+      <c r="K97">
         <v>1</v>
       </c>
-      <c r="L97" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M97" s="2" t="s">
+      <c r="L97" t="s">
+        <v>18</v>
+      </c>
+      <c r="M97" t="s">
         <v>141</v>
       </c>
-      <c r="N97" s="3">
+      <c r="N97" s="1">
         <v>46266</v>
       </c>
-      <c r="O97" s="2"/>
-      <c r="P97" s="3">
+      <c r="P97" s="1">
         <v>46355</v>
       </c>
     </row>
